--- a/Result/profitability/6949.xlsx
+++ b/Result/profitability/6949.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM17"/>
+  <dimension ref="A1:AM18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="F14" t="n">
-        <v>-56.46</v>
+        <v>-20.56</v>
       </c>
       <c r="G14" t="n">
         <v>-83</v>
@@ -2128,7 +2128,7 @@
         <v>-1.785</v>
       </c>
       <c r="N14" t="n">
-        <v>-76.78999999999999</v>
+        <v>-72.30249999999999</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -2161,10 +2161,10 @@
         <v>0.02307692307692299</v>
       </c>
       <c r="Y14" t="n">
-        <v>-91.88</v>
+        <v>-55.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>-2.594014680971203</v>
+        <v>-1.580463015245624</v>
       </c>
       <c r="AA14" t="n">
         <v>0.45</v>
@@ -2173,10 +2173,10 @@
         <v>-0.2528089887640449</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.009999999999998</v>
+        <v>38.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.05061375483437025</v>
+        <v>-0.6542794686396503</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2223,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="F15" t="n">
-        <v>-88.26000000000001</v>
+        <v>-116.2</v>
       </c>
       <c r="G15" t="n">
         <v>-125</v>
@@ -2255,7 +2255,7 @@
         <v>-1.7075</v>
       </c>
       <c r="N15" t="n">
-        <v>-58.68</v>
+        <v>-57.685</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0.518796992481203</v>
       </c>
       <c r="Y15" t="n">
-        <v>-31.8</v>
+        <v>-95.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.5632306057385761</v>
+        <v>4.651750972762646</v>
       </c>
       <c r="AA15" t="n">
         <v>-0.26</v>
@@ -2300,10 +2300,10 @@
         <v>0.1477272727272727</v>
       </c>
       <c r="AC15" t="n">
-        <v>-34.46000000000001</v>
+        <v>-62.40000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.6405204460966545</v>
+        <v>1.159851301115242</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>-1.765</v>
       </c>
       <c r="N16" t="n">
-        <v>-42.4125</v>
+        <v>-41.4175</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2415,10 +2415,10 @@
         <v>0.2821782178217822</v>
       </c>
       <c r="Y16" t="n">
-        <v>110.47</v>
+        <v>138.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>-1.251642873328801</v>
+        <v>-1.191135972461274</v>
       </c>
       <c r="AA16" t="n">
         <v>-0.8099999999999998</v>
@@ -2509,7 +2509,7 @@
         <v>-1.7175</v>
       </c>
       <c r="N17" t="n">
-        <v>-37.09625</v>
+        <v>-36.10125</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -2587,6 +2587,133 @@
       </c>
       <c r="AM17" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-20.09</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1221.13%</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-89</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1.665</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-31.17875</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1800000000000002</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.152542372881356</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.169999999999998</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.06183932346723031</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.02255639097744355</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.4699999999999989</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.02285992217898825</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
